--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2359,7 +2359,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-patient-contact-role</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-role-informateur-cisis</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelationType</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
